--- a/analysis_outputs/step_02/Table_08_Posthoc_Groupings.xlsx
+++ b/analysis_outputs/step_02/Table_08_Posthoc_Groupings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H325"/>
+  <dimension ref="A1:K325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,21 @@
           <t>Grouping_Letters</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Omnibus_p_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Omnibus_significant_p_lt_0_05</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Posthoc_interpreted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -505,6 +520,15 @@
           <t>cdef</t>
         </is>
       </c>
+      <c r="I2" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +565,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I3" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -577,6 +610,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -613,6 +655,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,6 +700,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -685,6 +745,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -721,6 +790,15 @@
           <t>ef</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -757,6 +835,15 @@
           <t>ef</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -793,6 +880,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -829,6 +925,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I11" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -865,6 +970,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -901,6 +1015,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -937,6 +1060,15 @@
           <t>f</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -973,6 +1105,15 @@
           <t>ef</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1009,6 +1150,15 @@
           <t>ef</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1045,6 +1195,15 @@
           <t>def</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1081,6 +1240,15 @@
           <t>bcdef</t>
         </is>
       </c>
+      <c r="I18" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1117,6 +1285,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1153,6 +1330,15 @@
           <t>ef</t>
         </is>
       </c>
+      <c r="I20" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1189,6 +1375,15 @@
           <t>ef</t>
         </is>
       </c>
+      <c r="I21" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1225,6 +1420,15 @@
           <t>def</t>
         </is>
       </c>
+      <c r="I22" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1261,6 +1465,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1297,6 +1510,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I24" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1333,6 +1555,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I25" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1369,6 +1600,15 @@
           <t>cdef</t>
         </is>
       </c>
+      <c r="I26" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1405,6 +1645,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1441,6 +1690,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I28" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1477,6 +1735,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I29" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1513,6 +1780,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I30" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1549,6 +1825,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I31" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1585,6 +1870,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I32" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1621,6 +1915,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I33" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1657,6 +1960,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I34" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1693,6 +2005,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I35" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1729,6 +2050,15 @@
           <t>abc</t>
         </is>
       </c>
+      <c r="I36" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1765,6 +2095,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I37" t="n">
+        <v>5.50811847483888e-07</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1801,6 +2140,15 @@
           <t>efghij</t>
         </is>
       </c>
+      <c r="I38" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1837,6 +2185,15 @@
           <t>bcdefgh</t>
         </is>
       </c>
+      <c r="I39" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1873,6 +2230,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I40" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1909,6 +2275,15 @@
           <t>abc</t>
         </is>
       </c>
+      <c r="I41" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1945,6 +2320,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I42" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1981,6 +2365,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I43" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2017,6 +2410,15 @@
           <t>ij</t>
         </is>
       </c>
+      <c r="I44" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2053,6 +2455,15 @@
           <t>ij</t>
         </is>
       </c>
+      <c r="I45" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2089,6 +2500,15 @@
           <t>cdefghij</t>
         </is>
       </c>
+      <c r="I46" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2125,6 +2545,15 @@
           <t>cdefghi</t>
         </is>
       </c>
+      <c r="I47" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2161,6 +2590,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I48" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2197,6 +2635,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I49" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2233,6 +2680,15 @@
           <t>j</t>
         </is>
       </c>
+      <c r="I50" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2269,6 +2725,15 @@
           <t>ij</t>
         </is>
       </c>
+      <c r="I51" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2305,6 +2770,15 @@
           <t>hij</t>
         </is>
       </c>
+      <c r="I52" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2341,6 +2815,15 @@
           <t>hij</t>
         </is>
       </c>
+      <c r="I53" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2377,6 +2860,15 @@
           <t>fghij</t>
         </is>
       </c>
+      <c r="I54" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2413,6 +2905,15 @@
           <t>defghij</t>
         </is>
       </c>
+      <c r="I55" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2449,6 +2950,15 @@
           <t>hij</t>
         </is>
       </c>
+      <c r="I56" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2485,6 +2995,15 @@
           <t>hij</t>
         </is>
       </c>
+      <c r="I57" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2521,6 +3040,15 @@
           <t>ghij</t>
         </is>
       </c>
+      <c r="I58" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2557,6 +3085,15 @@
           <t>efghij</t>
         </is>
       </c>
+      <c r="I59" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2593,6 +3130,15 @@
           <t>bcdefgh</t>
         </is>
       </c>
+      <c r="I60" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2629,6 +3175,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I61" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2665,6 +3220,15 @@
           <t>efghij</t>
         </is>
       </c>
+      <c r="I62" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2701,6 +3265,15 @@
           <t>cdefghij</t>
         </is>
       </c>
+      <c r="I63" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2737,6 +3310,15 @@
           <t>cdefghi</t>
         </is>
       </c>
+      <c r="I64" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J64" t="b">
+        <v>1</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2773,6 +3355,15 @@
           <t>bcdefgh</t>
         </is>
       </c>
+      <c r="I65" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2809,6 +3400,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I66" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2845,6 +3445,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I67" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2881,6 +3490,15 @@
           <t>bcdefgh</t>
         </is>
       </c>
+      <c r="I68" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2917,6 +3535,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I69" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2953,6 +3580,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I70" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2989,6 +3625,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I71" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3025,6 +3670,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I72" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J72" t="b">
+        <v>1</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3061,6 +3715,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I73" t="n">
+        <v>5.192968590027221e-11</v>
+      </c>
+      <c r="J73" t="b">
+        <v>1</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3097,6 +3760,15 @@
           <t>fghijklm</t>
         </is>
       </c>
+      <c r="I74" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J74" t="b">
+        <v>1</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3133,6 +3805,15 @@
           <t>abcdefghijk</t>
         </is>
       </c>
+      <c r="I75" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3169,6 +3850,15 @@
           <t>abcdefgh</t>
         </is>
       </c>
+      <c r="I76" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J76" t="b">
+        <v>1</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3205,6 +3895,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I77" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J77" t="b">
+        <v>1</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3241,6 +3940,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I78" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J78" t="b">
+        <v>1</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3277,6 +3985,15 @@
           <t>abc</t>
         </is>
       </c>
+      <c r="I79" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3313,6 +4030,15 @@
           <t>lm</t>
         </is>
       </c>
+      <c r="I80" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J80" t="b">
+        <v>1</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3349,6 +4075,15 @@
           <t>lm</t>
         </is>
       </c>
+      <c r="I81" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J81" t="b">
+        <v>1</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3385,6 +4120,15 @@
           <t>defghijklm</t>
         </is>
       </c>
+      <c r="I82" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J82" t="b">
+        <v>1</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3421,6 +4165,15 @@
           <t>bcdefghijkl</t>
         </is>
       </c>
+      <c r="I83" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3457,6 +4210,15 @@
           <t>abcdefghi</t>
         </is>
       </c>
+      <c r="I84" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J84" t="b">
+        <v>1</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3493,6 +4255,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I85" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J85" t="b">
+        <v>1</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3529,6 +4300,15 @@
           <t>m</t>
         </is>
       </c>
+      <c r="I86" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J86" t="b">
+        <v>1</v>
+      </c>
+      <c r="K86" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3565,6 +4345,15 @@
           <t>m</t>
         </is>
       </c>
+      <c r="I87" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J87" t="b">
+        <v>1</v>
+      </c>
+      <c r="K87" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3601,6 +4390,15 @@
           <t>klm</t>
         </is>
       </c>
+      <c r="I88" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J88" t="b">
+        <v>1</v>
+      </c>
+      <c r="K88" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3637,6 +4435,15 @@
           <t>jklm</t>
         </is>
       </c>
+      <c r="I89" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J89" t="b">
+        <v>1</v>
+      </c>
+      <c r="K89" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3673,6 +4480,15 @@
           <t>ghijklm</t>
         </is>
       </c>
+      <c r="I90" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J90" t="b">
+        <v>1</v>
+      </c>
+      <c r="K90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3709,6 +4525,15 @@
           <t>efghijklm</t>
         </is>
       </c>
+      <c r="I91" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J91" t="b">
+        <v>1</v>
+      </c>
+      <c r="K91" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3745,6 +4570,15 @@
           <t>ijklm</t>
         </is>
       </c>
+      <c r="I92" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J92" t="b">
+        <v>1</v>
+      </c>
+      <c r="K92" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3781,6 +4615,15 @@
           <t>klm</t>
         </is>
       </c>
+      <c r="I93" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J93" t="b">
+        <v>1</v>
+      </c>
+      <c r="K93" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3817,6 +4660,15 @@
           <t>hijklm</t>
         </is>
       </c>
+      <c r="I94" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J94" t="b">
+        <v>1</v>
+      </c>
+      <c r="K94" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3853,6 +4705,15 @@
           <t>defghijklm</t>
         </is>
       </c>
+      <c r="I95" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J95" t="b">
+        <v>1</v>
+      </c>
+      <c r="K95" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3889,6 +4750,15 @@
           <t>abcdefghijk</t>
         </is>
       </c>
+      <c r="I96" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J96" t="b">
+        <v>1</v>
+      </c>
+      <c r="K96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3925,6 +4795,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I97" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J97" t="b">
+        <v>1</v>
+      </c>
+      <c r="K97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3961,6 +4840,15 @@
           <t>ijklm</t>
         </is>
       </c>
+      <c r="I98" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J98" t="b">
+        <v>1</v>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3997,6 +4885,15 @@
           <t>cdefghijklm</t>
         </is>
       </c>
+      <c r="I99" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J99" t="b">
+        <v>1</v>
+      </c>
+      <c r="K99" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4033,6 +4930,15 @@
           <t>cdefghijklm</t>
         </is>
       </c>
+      <c r="I100" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J100" t="b">
+        <v>1</v>
+      </c>
+      <c r="K100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4069,6 +4975,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I101" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J101" t="b">
+        <v>1</v>
+      </c>
+      <c r="K101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4105,6 +5020,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I102" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J102" t="b">
+        <v>1</v>
+      </c>
+      <c r="K102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4141,6 +5065,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I103" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J103" t="b">
+        <v>1</v>
+      </c>
+      <c r="K103" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4177,6 +5110,15 @@
           <t>abcdefghijk</t>
         </is>
       </c>
+      <c r="I104" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J104" t="b">
+        <v>1</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4213,6 +5155,15 @@
           <t>abcdefgh</t>
         </is>
       </c>
+      <c r="I105" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J105" t="b">
+        <v>1</v>
+      </c>
+      <c r="K105" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4249,6 +5200,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I106" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J106" t="b">
+        <v>1</v>
+      </c>
+      <c r="K106" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4285,6 +5245,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I107" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J107" t="b">
+        <v>1</v>
+      </c>
+      <c r="K107" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4321,6 +5290,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I108" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J108" t="b">
+        <v>1</v>
+      </c>
+      <c r="K108" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4357,6 +5335,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I109" t="n">
+        <v>1.43001591743226e-10</v>
+      </c>
+      <c r="J109" t="b">
+        <v>1</v>
+      </c>
+      <c r="K109" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4393,6 +5380,15 @@
           <t>defg</t>
         </is>
       </c>
+      <c r="I110" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J110" t="b">
+        <v>1</v>
+      </c>
+      <c r="K110" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4429,6 +5425,15 @@
           <t>cdefg</t>
         </is>
       </c>
+      <c r="I111" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J111" t="b">
+        <v>1</v>
+      </c>
+      <c r="K111" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4465,6 +5470,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I112" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J112" t="b">
+        <v>1</v>
+      </c>
+      <c r="K112" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4501,6 +5515,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I113" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J113" t="b">
+        <v>1</v>
+      </c>
+      <c r="K113" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4537,6 +5560,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I114" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J114" t="b">
+        <v>1</v>
+      </c>
+      <c r="K114" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4573,6 +5605,15 @@
           <t>abc</t>
         </is>
       </c>
+      <c r="I115" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J115" t="b">
+        <v>1</v>
+      </c>
+      <c r="K115" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4609,6 +5650,15 @@
           <t>efg</t>
         </is>
       </c>
+      <c r="I116" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J116" t="b">
+        <v>1</v>
+      </c>
+      <c r="K116" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4645,6 +5695,15 @@
           <t>g</t>
         </is>
       </c>
+      <c r="I117" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J117" t="b">
+        <v>1</v>
+      </c>
+      <c r="K117" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4681,6 +5740,15 @@
           <t>efg</t>
         </is>
       </c>
+      <c r="I118" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J118" t="b">
+        <v>1</v>
+      </c>
+      <c r="K118" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4717,6 +5785,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I119" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J119" t="b">
+        <v>1</v>
+      </c>
+      <c r="K119" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4753,6 +5830,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I120" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J120" t="b">
+        <v>1</v>
+      </c>
+      <c r="K120" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4789,6 +5875,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I121" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J121" t="b">
+        <v>1</v>
+      </c>
+      <c r="K121" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4825,6 +5920,15 @@
           <t>efg</t>
         </is>
       </c>
+      <c r="I122" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J122" t="b">
+        <v>1</v>
+      </c>
+      <c r="K122" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4861,6 +5965,15 @@
           <t>efg</t>
         </is>
       </c>
+      <c r="I123" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J123" t="b">
+        <v>1</v>
+      </c>
+      <c r="K123" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4897,6 +6010,15 @@
           <t>fg</t>
         </is>
       </c>
+      <c r="I124" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J124" t="b">
+        <v>1</v>
+      </c>
+      <c r="K124" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4933,6 +6055,15 @@
           <t>efg</t>
         </is>
       </c>
+      <c r="I125" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J125" t="b">
+        <v>1</v>
+      </c>
+      <c r="K125" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4969,6 +6100,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I126" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J126" t="b">
+        <v>1</v>
+      </c>
+      <c r="K126" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5005,6 +6145,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I127" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J127" t="b">
+        <v>1</v>
+      </c>
+      <c r="K127" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5041,6 +6190,15 @@
           <t>efg</t>
         </is>
       </c>
+      <c r="I128" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J128" t="b">
+        <v>1</v>
+      </c>
+      <c r="K128" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5077,6 +6235,15 @@
           <t>defg</t>
         </is>
       </c>
+      <c r="I129" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J129" t="b">
+        <v>1</v>
+      </c>
+      <c r="K129" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5113,6 +6280,15 @@
           <t>defg</t>
         </is>
       </c>
+      <c r="I130" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J130" t="b">
+        <v>1</v>
+      </c>
+      <c r="K130" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5149,6 +6325,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I131" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J131" t="b">
+        <v>1</v>
+      </c>
+      <c r="K131" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5185,6 +6370,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I132" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J132" t="b">
+        <v>1</v>
+      </c>
+      <c r="K132" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5221,6 +6415,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I133" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J133" t="b">
+        <v>1</v>
+      </c>
+      <c r="K133" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5257,6 +6460,15 @@
           <t>bcdefg</t>
         </is>
       </c>
+      <c r="I134" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J134" t="b">
+        <v>1</v>
+      </c>
+      <c r="K134" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5293,6 +6505,15 @@
           <t>defg</t>
         </is>
       </c>
+      <c r="I135" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J135" t="b">
+        <v>1</v>
+      </c>
+      <c r="K135" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5329,6 +6550,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I136" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J136" t="b">
+        <v>1</v>
+      </c>
+      <c r="K136" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5365,6 +6595,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I137" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J137" t="b">
+        <v>1</v>
+      </c>
+      <c r="K137" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5401,6 +6640,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I138" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J138" t="b">
+        <v>1</v>
+      </c>
+      <c r="K138" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5437,6 +6685,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I139" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J139" t="b">
+        <v>1</v>
+      </c>
+      <c r="K139" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5473,6 +6730,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I140" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J140" t="b">
+        <v>1</v>
+      </c>
+      <c r="K140" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5509,6 +6775,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I141" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J141" t="b">
+        <v>1</v>
+      </c>
+      <c r="K141" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5545,6 +6820,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I142" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J142" t="b">
+        <v>1</v>
+      </c>
+      <c r="K142" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5581,6 +6865,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I143" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J143" t="b">
+        <v>1</v>
+      </c>
+      <c r="K143" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5617,6 +6910,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I144" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J144" t="b">
+        <v>1</v>
+      </c>
+      <c r="K144" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5653,6 +6955,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I145" t="n">
+        <v>4.294382094017315e-07</v>
+      </c>
+      <c r="J145" t="b">
+        <v>1</v>
+      </c>
+      <c r="K145" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5689,6 +7000,15 @@
           <t>cdefghij</t>
         </is>
       </c>
+      <c r="I146" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J146" t="b">
+        <v>1</v>
+      </c>
+      <c r="K146" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5725,6 +7045,15 @@
           <t>bcdefghij</t>
         </is>
       </c>
+      <c r="I147" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J147" t="b">
+        <v>1</v>
+      </c>
+      <c r="K147" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5761,6 +7090,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I148" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J148" t="b">
+        <v>1</v>
+      </c>
+      <c r="K148" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5797,6 +7135,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I149" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J149" t="b">
+        <v>1</v>
+      </c>
+      <c r="K149" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5833,6 +7180,15 @@
           <t>abc</t>
         </is>
       </c>
+      <c r="I150" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J150" t="b">
+        <v>1</v>
+      </c>
+      <c r="K150" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5869,6 +7225,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I151" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J151" t="b">
+        <v>1</v>
+      </c>
+      <c r="K151" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5905,6 +7270,15 @@
           <t>ij</t>
         </is>
       </c>
+      <c r="I152" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J152" t="b">
+        <v>1</v>
+      </c>
+      <c r="K152" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5941,6 +7315,15 @@
           <t>hij</t>
         </is>
       </c>
+      <c r="I153" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J153" t="b">
+        <v>1</v>
+      </c>
+      <c r="K153" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5977,6 +7360,15 @@
           <t>efghij</t>
         </is>
       </c>
+      <c r="I154" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J154" t="b">
+        <v>1</v>
+      </c>
+      <c r="K154" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6013,6 +7405,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I155" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J155" t="b">
+        <v>1</v>
+      </c>
+      <c r="K155" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6049,6 +7450,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I156" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J156" t="b">
+        <v>1</v>
+      </c>
+      <c r="K156" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6085,6 +7495,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I157" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J157" t="b">
+        <v>1</v>
+      </c>
+      <c r="K157" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6121,6 +7540,15 @@
           <t>ij</t>
         </is>
       </c>
+      <c r="I158" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J158" t="b">
+        <v>1</v>
+      </c>
+      <c r="K158" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6157,6 +7585,15 @@
           <t>j</t>
         </is>
       </c>
+      <c r="I159" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J159" t="b">
+        <v>1</v>
+      </c>
+      <c r="K159" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6193,6 +7630,15 @@
           <t>hij</t>
         </is>
       </c>
+      <c r="I160" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J160" t="b">
+        <v>1</v>
+      </c>
+      <c r="K160" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6229,6 +7675,15 @@
           <t>fghij</t>
         </is>
       </c>
+      <c r="I161" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J161" t="b">
+        <v>1</v>
+      </c>
+      <c r="K161" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6265,6 +7720,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I162" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J162" t="b">
+        <v>1</v>
+      </c>
+      <c r="K162" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6301,6 +7765,15 @@
           <t>abcdefgh</t>
         </is>
       </c>
+      <c r="I163" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J163" t="b">
+        <v>1</v>
+      </c>
+      <c r="K163" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6337,6 +7810,15 @@
           <t>ghij</t>
         </is>
       </c>
+      <c r="I164" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J164" t="b">
+        <v>1</v>
+      </c>
+      <c r="K164" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6373,6 +7855,15 @@
           <t>efghij</t>
         </is>
       </c>
+      <c r="I165" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J165" t="b">
+        <v>1</v>
+      </c>
+      <c r="K165" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6409,6 +7900,15 @@
           <t>cdefghij</t>
         </is>
       </c>
+      <c r="I166" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J166" t="b">
+        <v>1</v>
+      </c>
+      <c r="K166" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6445,6 +7945,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I167" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J167" t="b">
+        <v>1</v>
+      </c>
+      <c r="K167" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6481,6 +7990,15 @@
           <t>abcdefghi</t>
         </is>
       </c>
+      <c r="I168" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J168" t="b">
+        <v>1</v>
+      </c>
+      <c r="K168" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6517,6 +8035,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I169" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J169" t="b">
+        <v>1</v>
+      </c>
+      <c r="K169" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6553,6 +8080,15 @@
           <t>defghij</t>
         </is>
       </c>
+      <c r="I170" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J170" t="b">
+        <v>1</v>
+      </c>
+      <c r="K170" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6589,6 +8125,15 @@
           <t>efghij</t>
         </is>
       </c>
+      <c r="I171" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J171" t="b">
+        <v>1</v>
+      </c>
+      <c r="K171" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6625,6 +8170,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I172" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J172" t="b">
+        <v>1</v>
+      </c>
+      <c r="K172" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6661,6 +8215,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I173" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J173" t="b">
+        <v>1</v>
+      </c>
+      <c r="K173" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6697,6 +8260,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I174" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J174" t="b">
+        <v>1</v>
+      </c>
+      <c r="K174" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6733,6 +8305,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I175" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J175" t="b">
+        <v>1</v>
+      </c>
+      <c r="K175" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6769,6 +8350,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I176" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J176" t="b">
+        <v>1</v>
+      </c>
+      <c r="K176" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6805,6 +8395,15 @@
           <t>abcdefghij</t>
         </is>
       </c>
+      <c r="I177" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J177" t="b">
+        <v>1</v>
+      </c>
+      <c r="K177" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6841,6 +8440,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I178" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J178" t="b">
+        <v>1</v>
+      </c>
+      <c r="K178" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6877,6 +8485,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I179" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J179" t="b">
+        <v>1</v>
+      </c>
+      <c r="K179" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6913,6 +8530,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I180" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J180" t="b">
+        <v>1</v>
+      </c>
+      <c r="K180" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6949,6 +8575,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I181" t="n">
+        <v>5.150350749945782e-09</v>
+      </c>
+      <c r="J181" t="b">
+        <v>1</v>
+      </c>
+      <c r="K181" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6985,6 +8620,15 @@
           <t>cdefghi</t>
         </is>
       </c>
+      <c r="I182" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J182" t="b">
+        <v>1</v>
+      </c>
+      <c r="K182" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7021,6 +8665,15 @@
           <t>bcdefghi</t>
         </is>
       </c>
+      <c r="I183" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J183" t="b">
+        <v>1</v>
+      </c>
+      <c r="K183" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7057,6 +8710,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I184" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J184" t="b">
+        <v>1</v>
+      </c>
+      <c r="K184" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7093,6 +8755,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I185" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J185" t="b">
+        <v>1</v>
+      </c>
+      <c r="K185" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7129,6 +8800,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I186" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J186" t="b">
+        <v>1</v>
+      </c>
+      <c r="K186" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7165,6 +8845,15 @@
           <t>ab</t>
         </is>
       </c>
+      <c r="I187" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J187" t="b">
+        <v>1</v>
+      </c>
+      <c r="K187" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7201,6 +8890,15 @@
           <t>hi</t>
         </is>
       </c>
+      <c r="I188" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J188" t="b">
+        <v>1</v>
+      </c>
+      <c r="K188" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7237,6 +8935,15 @@
           <t>hi</t>
         </is>
       </c>
+      <c r="I189" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J189" t="b">
+        <v>1</v>
+      </c>
+      <c r="K189" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7273,6 +8980,15 @@
           <t>defghi</t>
         </is>
       </c>
+      <c r="I190" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J190" t="b">
+        <v>1</v>
+      </c>
+      <c r="K190" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7309,6 +9025,15 @@
           <t>abcdefghi</t>
         </is>
       </c>
+      <c r="I191" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J191" t="b">
+        <v>1</v>
+      </c>
+      <c r="K191" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7345,6 +9070,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I192" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J192" t="b">
+        <v>1</v>
+      </c>
+      <c r="K192" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7381,6 +9115,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I193" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J193" t="b">
+        <v>1</v>
+      </c>
+      <c r="K193" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7417,6 +9160,15 @@
           <t>i</t>
         </is>
       </c>
+      <c r="I194" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J194" t="b">
+        <v>1</v>
+      </c>
+      <c r="K194" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7453,6 +9205,15 @@
           <t>hi</t>
         </is>
       </c>
+      <c r="I195" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J195" t="b">
+        <v>1</v>
+      </c>
+      <c r="K195" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7489,6 +9250,15 @@
           <t>ghi</t>
         </is>
       </c>
+      <c r="I196" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J196" t="b">
+        <v>1</v>
+      </c>
+      <c r="K196" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7525,6 +9295,15 @@
           <t>cdefghi</t>
         </is>
       </c>
+      <c r="I197" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J197" t="b">
+        <v>1</v>
+      </c>
+      <c r="K197" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7561,6 +9340,15 @@
           <t>bcdefghi</t>
         </is>
       </c>
+      <c r="I198" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J198" t="b">
+        <v>1</v>
+      </c>
+      <c r="K198" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7597,6 +9385,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I199" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J199" t="b">
+        <v>1</v>
+      </c>
+      <c r="K199" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7633,6 +9430,15 @@
           <t>fghi</t>
         </is>
       </c>
+      <c r="I200" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J200" t="b">
+        <v>1</v>
+      </c>
+      <c r="K200" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7669,6 +9475,15 @@
           <t>efghi</t>
         </is>
       </c>
+      <c r="I201" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J201" t="b">
+        <v>1</v>
+      </c>
+      <c r="K201" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7705,6 +9520,15 @@
           <t>cdefghi</t>
         </is>
       </c>
+      <c r="I202" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J202" t="b">
+        <v>1</v>
+      </c>
+      <c r="K202" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7741,6 +9565,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I203" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J203" t="b">
+        <v>1</v>
+      </c>
+      <c r="K203" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7777,6 +9610,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I204" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J204" t="b">
+        <v>1</v>
+      </c>
+      <c r="K204" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7813,6 +9655,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I205" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J205" t="b">
+        <v>1</v>
+      </c>
+      <c r="K205" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7849,6 +9700,15 @@
           <t>defghi</t>
         </is>
       </c>
+      <c r="I206" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J206" t="b">
+        <v>1</v>
+      </c>
+      <c r="K206" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7885,6 +9745,15 @@
           <t>cdefghi</t>
         </is>
       </c>
+      <c r="I207" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J207" t="b">
+        <v>1</v>
+      </c>
+      <c r="K207" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7921,6 +9790,15 @@
           <t>abcdefghi</t>
         </is>
       </c>
+      <c r="I208" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J208" t="b">
+        <v>1</v>
+      </c>
+      <c r="K208" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7957,6 +9835,15 @@
           <t>abcdefg</t>
         </is>
       </c>
+      <c r="I209" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J209" t="b">
+        <v>1</v>
+      </c>
+      <c r="K209" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7993,6 +9880,15 @@
           <t>abcde</t>
         </is>
       </c>
+      <c r="I210" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J210" t="b">
+        <v>1</v>
+      </c>
+      <c r="K210" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8029,6 +9925,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I211" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J211" t="b">
+        <v>1</v>
+      </c>
+      <c r="K211" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8065,6 +9970,15 @@
           <t>abcdefghi</t>
         </is>
       </c>
+      <c r="I212" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J212" t="b">
+        <v>1</v>
+      </c>
+      <c r="K212" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8101,6 +10015,15 @@
           <t>abcdefgh</t>
         </is>
       </c>
+      <c r="I213" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J213" t="b">
+        <v>1</v>
+      </c>
+      <c r="K213" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8137,6 +10060,15 @@
           <t>abcdef</t>
         </is>
       </c>
+      <c r="I214" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J214" t="b">
+        <v>1</v>
+      </c>
+      <c r="K214" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8173,6 +10105,15 @@
           <t>abcd</t>
         </is>
       </c>
+      <c r="I215" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J215" t="b">
+        <v>1</v>
+      </c>
+      <c r="K215" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8209,6 +10150,15 @@
           <t>abc</t>
         </is>
       </c>
+      <c r="I216" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J216" t="b">
+        <v>1</v>
+      </c>
+      <c r="K216" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8245,6 +10195,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I217" t="n">
+        <v>8.502627440347e-09</v>
+      </c>
+      <c r="J217" t="b">
+        <v>1</v>
+      </c>
+      <c r="K217" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8281,6 +10240,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I218" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J218" t="b">
+        <v>1</v>
+      </c>
+      <c r="K218" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8317,6 +10285,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I219" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J219" t="b">
+        <v>1</v>
+      </c>
+      <c r="K219" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8353,6 +10330,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I220" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J220" t="b">
+        <v>1</v>
+      </c>
+      <c r="K220" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8389,6 +10375,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I221" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J221" t="b">
+        <v>1</v>
+      </c>
+      <c r="K221" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8425,6 +10420,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I222" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J222" t="b">
+        <v>1</v>
+      </c>
+      <c r="K222" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8461,6 +10465,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I223" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J223" t="b">
+        <v>1</v>
+      </c>
+      <c r="K223" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8497,6 +10510,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I224" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J224" t="b">
+        <v>1</v>
+      </c>
+      <c r="K224" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8533,6 +10555,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I225" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J225" t="b">
+        <v>1</v>
+      </c>
+      <c r="K225" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8569,6 +10600,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I226" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J226" t="b">
+        <v>1</v>
+      </c>
+      <c r="K226" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8605,6 +10645,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I227" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J227" t="b">
+        <v>1</v>
+      </c>
+      <c r="K227" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8641,6 +10690,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I228" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J228" t="b">
+        <v>1</v>
+      </c>
+      <c r="K228" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8677,6 +10735,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I229" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J229" t="b">
+        <v>1</v>
+      </c>
+      <c r="K229" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8713,6 +10780,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I230" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J230" t="b">
+        <v>1</v>
+      </c>
+      <c r="K230" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8749,6 +10825,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I231" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J231" t="b">
+        <v>1</v>
+      </c>
+      <c r="K231" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8785,6 +10870,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I232" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J232" t="b">
+        <v>1</v>
+      </c>
+      <c r="K232" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8821,6 +10915,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I233" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J233" t="b">
+        <v>1</v>
+      </c>
+      <c r="K233" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8857,6 +10960,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I234" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J234" t="b">
+        <v>1</v>
+      </c>
+      <c r="K234" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8893,6 +11005,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I235" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J235" t="b">
+        <v>1</v>
+      </c>
+      <c r="K235" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8929,6 +11050,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I236" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J236" t="b">
+        <v>1</v>
+      </c>
+      <c r="K236" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8965,6 +11095,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I237" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J237" t="b">
+        <v>1</v>
+      </c>
+      <c r="K237" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9001,6 +11140,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I238" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J238" t="b">
+        <v>1</v>
+      </c>
+      <c r="K238" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9037,6 +11185,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I239" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J239" t="b">
+        <v>1</v>
+      </c>
+      <c r="K239" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9073,6 +11230,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I240" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J240" t="b">
+        <v>1</v>
+      </c>
+      <c r="K240" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9109,6 +11275,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I241" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J241" t="b">
+        <v>1</v>
+      </c>
+      <c r="K241" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9145,6 +11320,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I242" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J242" t="b">
+        <v>1</v>
+      </c>
+      <c r="K242" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9181,6 +11365,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I243" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J243" t="b">
+        <v>1</v>
+      </c>
+      <c r="K243" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9217,6 +11410,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I244" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J244" t="b">
+        <v>1</v>
+      </c>
+      <c r="K244" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9253,6 +11455,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I245" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J245" t="b">
+        <v>1</v>
+      </c>
+      <c r="K245" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9289,6 +11500,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I246" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J246" t="b">
+        <v>1</v>
+      </c>
+      <c r="K246" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9325,6 +11545,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I247" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J247" t="b">
+        <v>1</v>
+      </c>
+      <c r="K247" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9361,6 +11590,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I248" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J248" t="b">
+        <v>1</v>
+      </c>
+      <c r="K248" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9397,6 +11635,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I249" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J249" t="b">
+        <v>1</v>
+      </c>
+      <c r="K249" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9433,6 +11680,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I250" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J250" t="b">
+        <v>1</v>
+      </c>
+      <c r="K250" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9469,6 +11725,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I251" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J251" t="b">
+        <v>1</v>
+      </c>
+      <c r="K251" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9505,6 +11770,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I252" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J252" t="b">
+        <v>1</v>
+      </c>
+      <c r="K252" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9541,6 +11815,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I253" t="n">
+        <v>0.003201216236313163</v>
+      </c>
+      <c r="J253" t="b">
+        <v>1</v>
+      </c>
+      <c r="K253" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9577,6 +11860,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I254" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J254" t="b">
+        <v>0</v>
+      </c>
+      <c r="K254" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9613,6 +11905,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I255" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J255" t="b">
+        <v>0</v>
+      </c>
+      <c r="K255" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9649,6 +11950,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I256" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J256" t="b">
+        <v>0</v>
+      </c>
+      <c r="K256" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9685,6 +11995,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I257" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J257" t="b">
+        <v>0</v>
+      </c>
+      <c r="K257" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9721,6 +12040,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I258" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J258" t="b">
+        <v>0</v>
+      </c>
+      <c r="K258" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9757,6 +12085,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I259" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J259" t="b">
+        <v>0</v>
+      </c>
+      <c r="K259" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9793,6 +12130,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I260" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J260" t="b">
+        <v>0</v>
+      </c>
+      <c r="K260" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9829,6 +12175,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I261" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J261" t="b">
+        <v>0</v>
+      </c>
+      <c r="K261" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9865,6 +12220,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I262" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J262" t="b">
+        <v>0</v>
+      </c>
+      <c r="K262" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9901,6 +12265,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I263" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J263" t="b">
+        <v>0</v>
+      </c>
+      <c r="K263" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9937,6 +12310,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I264" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J264" t="b">
+        <v>0</v>
+      </c>
+      <c r="K264" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9973,6 +12355,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I265" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J265" t="b">
+        <v>0</v>
+      </c>
+      <c r="K265" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -10009,6 +12400,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I266" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J266" t="b">
+        <v>0</v>
+      </c>
+      <c r="K266" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10045,6 +12445,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I267" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J267" t="b">
+        <v>0</v>
+      </c>
+      <c r="K267" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10081,6 +12490,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I268" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J268" t="b">
+        <v>0</v>
+      </c>
+      <c r="K268" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10117,6 +12535,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I269" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J269" t="b">
+        <v>0</v>
+      </c>
+      <c r="K269" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10153,6 +12580,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I270" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J270" t="b">
+        <v>0</v>
+      </c>
+      <c r="K270" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10189,6 +12625,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I271" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J271" t="b">
+        <v>0</v>
+      </c>
+      <c r="K271" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10225,6 +12670,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I272" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J272" t="b">
+        <v>0</v>
+      </c>
+      <c r="K272" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10261,6 +12715,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I273" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J273" t="b">
+        <v>0</v>
+      </c>
+      <c r="K273" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10297,6 +12760,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I274" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J274" t="b">
+        <v>0</v>
+      </c>
+      <c r="K274" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10333,6 +12805,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I275" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J275" t="b">
+        <v>0</v>
+      </c>
+      <c r="K275" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10369,6 +12850,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I276" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J276" t="b">
+        <v>0</v>
+      </c>
+      <c r="K276" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10405,6 +12895,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I277" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J277" t="b">
+        <v>0</v>
+      </c>
+      <c r="K277" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10441,6 +12940,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I278" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J278" t="b">
+        <v>0</v>
+      </c>
+      <c r="K278" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10477,6 +12985,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I279" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J279" t="b">
+        <v>0</v>
+      </c>
+      <c r="K279" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10513,6 +13030,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I280" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J280" t="b">
+        <v>0</v>
+      </c>
+      <c r="K280" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10549,6 +13075,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I281" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J281" t="b">
+        <v>0</v>
+      </c>
+      <c r="K281" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10585,6 +13120,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I282" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J282" t="b">
+        <v>0</v>
+      </c>
+      <c r="K282" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10621,6 +13165,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I283" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J283" t="b">
+        <v>0</v>
+      </c>
+      <c r="K283" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10657,6 +13210,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I284" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J284" t="b">
+        <v>0</v>
+      </c>
+      <c r="K284" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10693,6 +13255,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I285" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J285" t="b">
+        <v>0</v>
+      </c>
+      <c r="K285" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10729,6 +13300,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I286" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J286" t="b">
+        <v>0</v>
+      </c>
+      <c r="K286" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10765,6 +13345,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I287" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J287" t="b">
+        <v>0</v>
+      </c>
+      <c r="K287" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10801,6 +13390,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I288" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J288" t="b">
+        <v>0</v>
+      </c>
+      <c r="K288" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10837,6 +13435,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I289" t="n">
+        <v>0.05569451743392675</v>
+      </c>
+      <c r="J289" t="b">
+        <v>0</v>
+      </c>
+      <c r="K289" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10873,6 +13480,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I290" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J290" t="b">
+        <v>0</v>
+      </c>
+      <c r="K290" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10909,6 +13525,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I291" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J291" t="b">
+        <v>0</v>
+      </c>
+      <c r="K291" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10945,6 +13570,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I292" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J292" t="b">
+        <v>0</v>
+      </c>
+      <c r="K292" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10981,6 +13615,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I293" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J293" t="b">
+        <v>0</v>
+      </c>
+      <c r="K293" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -11017,6 +13660,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I294" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J294" t="b">
+        <v>0</v>
+      </c>
+      <c r="K294" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11053,6 +13705,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I295" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J295" t="b">
+        <v>0</v>
+      </c>
+      <c r="K295" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11089,6 +13750,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I296" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J296" t="b">
+        <v>0</v>
+      </c>
+      <c r="K296" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11125,6 +13795,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I297" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J297" t="b">
+        <v>0</v>
+      </c>
+      <c r="K297" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11161,6 +13840,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I298" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J298" t="b">
+        <v>0</v>
+      </c>
+      <c r="K298" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11197,6 +13885,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I299" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J299" t="b">
+        <v>0</v>
+      </c>
+      <c r="K299" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11233,6 +13930,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I300" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J300" t="b">
+        <v>0</v>
+      </c>
+      <c r="K300" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11269,6 +13975,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I301" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J301" t="b">
+        <v>0</v>
+      </c>
+      <c r="K301" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11305,6 +14020,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I302" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J302" t="b">
+        <v>0</v>
+      </c>
+      <c r="K302" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11341,6 +14065,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I303" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J303" t="b">
+        <v>0</v>
+      </c>
+      <c r="K303" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11377,6 +14110,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I304" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J304" t="b">
+        <v>0</v>
+      </c>
+      <c r="K304" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11413,6 +14155,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I305" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J305" t="b">
+        <v>0</v>
+      </c>
+      <c r="K305" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11449,6 +14200,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I306" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J306" t="b">
+        <v>0</v>
+      </c>
+      <c r="K306" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11485,6 +14245,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I307" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J307" t="b">
+        <v>0</v>
+      </c>
+      <c r="K307" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11521,6 +14290,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I308" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J308" t="b">
+        <v>0</v>
+      </c>
+      <c r="K308" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11557,6 +14335,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I309" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J309" t="b">
+        <v>0</v>
+      </c>
+      <c r="K309" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11593,6 +14380,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I310" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J310" t="b">
+        <v>0</v>
+      </c>
+      <c r="K310" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11629,6 +14425,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I311" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J311" t="b">
+        <v>0</v>
+      </c>
+      <c r="K311" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11665,6 +14470,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I312" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J312" t="b">
+        <v>0</v>
+      </c>
+      <c r="K312" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11701,6 +14515,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I313" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J313" t="b">
+        <v>0</v>
+      </c>
+      <c r="K313" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11737,6 +14560,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I314" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J314" t="b">
+        <v>0</v>
+      </c>
+      <c r="K314" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11773,6 +14605,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I315" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J315" t="b">
+        <v>0</v>
+      </c>
+      <c r="K315" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11809,6 +14650,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I316" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J316" t="b">
+        <v>0</v>
+      </c>
+      <c r="K316" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11845,6 +14695,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I317" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J317" t="b">
+        <v>0</v>
+      </c>
+      <c r="K317" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11881,6 +14740,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I318" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J318" t="b">
+        <v>0</v>
+      </c>
+      <c r="K318" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11917,6 +14785,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I319" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J319" t="b">
+        <v>0</v>
+      </c>
+      <c r="K319" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11953,6 +14830,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I320" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J320" t="b">
+        <v>0</v>
+      </c>
+      <c r="K320" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11989,6 +14875,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I321" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J321" t="b">
+        <v>0</v>
+      </c>
+      <c r="K321" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12025,6 +14920,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I322" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J322" t="b">
+        <v>0</v>
+      </c>
+      <c r="K322" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12061,6 +14965,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I323" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J323" t="b">
+        <v>0</v>
+      </c>
+      <c r="K323" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12097,6 +15010,15 @@
           <t>a</t>
         </is>
       </c>
+      <c r="I324" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J324" t="b">
+        <v>0</v>
+      </c>
+      <c r="K324" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12132,6 +15054,15 @@
         <is>
           <t>a</t>
         </is>
+      </c>
+      <c r="I325" t="n">
+        <v>0.5089791919988667</v>
+      </c>
+      <c r="J325" t="b">
+        <v>0</v>
+      </c>
+      <c r="K325" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
